--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1257,7 +1257,11 @@
           <t>Position in Class:</t>
         </is>
       </c>
-      <c r="M20" s="39" t="inlineStr"/>
+      <c r="M20" s="39" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
       <c r="N20" s="30" t="n"/>
       <c r="O20" s="30" t="n"/>
       <c r="P20" s="30" t="n"/>
@@ -1511,11 +1515,11 @@
         <v>14</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1569,14 +1573,14 @@
       <c r="E29" s="35" t="n"/>
       <c r="F29" s="36" t="n"/>
       <c r="G29" s="42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" s="42" t="n">
         <v>12</v>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="42" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K29" s="36" t="n"/>
       <c r="L29" s="18">
@@ -1591,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -1870,16 +1874,32 @@
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
-      <c r="G35" s="18" t="inlineStr"/>
-      <c r="H35" s="18" t="inlineStr"/>
+      <c r="G35" s="42" t="n">
+        <v>13</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>13</v>
+      </c>
       <c r="I35" s="36" t="n"/>
-      <c r="J35" s="18" t="inlineStr"/>
+      <c r="J35" s="42" t="n">
+        <v>39</v>
+      </c>
       <c r="K35" s="36" t="n"/>
-      <c r="L35" s="18" t="inlineStr"/>
+      <c r="L35" s="18">
+        <f>SUM(G35, H35, J35)</f>
+        <v/>
+      </c>
       <c r="M35" s="36" t="n"/>
-      <c r="N35" s="18" t="inlineStr"/>
+      <c r="N35" s="18">
+        <f>IF(L35&gt;=75,"A1",IF(L35&gt;=70,"B2",IF(L35&gt;=65,"B3",IF(L35&gt;=60,"C4",IF(L35&gt;=55,"C5",IF(L35&gt;=50,"C6",IF(L35&gt;=45,"D7",IF(L35&gt;=40,"E8","F9"))))))))</f>
+        <v/>
+      </c>
       <c r="O35" s="36" t="n"/>
-      <c r="P35" s="18" t="inlineStr"/>
+      <c r="P35" s="42" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
       <c r="Q35" s="35" t="n"/>
       <c r="R35" s="36" t="n"/>
       <c r="T35" s="18" t="inlineStr">
@@ -1996,7 +2016,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>601</v>
+        <v>675</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2018,11 +2038,11 @@
         <v>16</v>
       </c>
       <c r="H39" s="42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="42" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K39" s="36" t="n"/>
       <c r="L39" s="18">
@@ -2037,7 +2057,7 @@
       <c r="O39" s="36" t="n"/>
       <c r="P39" s="42" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="Q39" s="35" t="n"/>
@@ -2048,7 +2068,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2085,7 +2105,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>75.12%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2150,7 +2170,7 @@
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="42" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" s="36" t="n"/>
       <c r="L42" s="18">
@@ -2175,7 +2195,11 @@
           <t>Position in Class</t>
         </is>
       </c>
-      <c r="X42" s="43" t="inlineStr"/>
+      <c r="X42" s="43" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
       <c r="Y42" s="30" t="n"/>
       <c r="Z42" s="30" t="n"/>
     </row>
@@ -2196,7 +2220,7 @@
         <v>14</v>
       </c>
       <c r="H43" s="42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I43" s="36" t="n"/>
       <c r="J43" s="42" t="n">
@@ -2262,7 +2286,7 @@
         </is>
       </c>
       <c r="X44" s="43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y44" s="30" t="n"/>
       <c r="Z44" s="30" t="n"/>
@@ -2324,7 +2348,7 @@
       </c>
       <c r="I46" s="36" t="n"/>
       <c r="J46" s="42" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K46" s="36" t="n"/>
       <c r="L46" s="18">
@@ -2410,7 +2434,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>601</v>
+        <v>675</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2442,7 +2466,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2475,7 +2499,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>75.12%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2541,7 +2565,11 @@
       <c r="D52" s="35" t="n"/>
       <c r="E52" s="35" t="n"/>
       <c r="F52" s="36" t="n"/>
-      <c r="G52" s="44" t="inlineStr"/>
+      <c r="G52" s="44" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="35" t="n"/>
       <c r="J52" s="35" t="n"/>
@@ -2592,7 +2620,7 @@
       <c r="E54" s="35" t="n"/>
       <c r="F54" s="36" t="n"/>
       <c r="G54" s="44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H54" s="35" t="n"/>
       <c r="I54" s="35" t="n"/>

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1512,14 +1512,14 @@
       <c r="E28" s="35" t="n"/>
       <c r="F28" s="36" t="n"/>
       <c r="G28" s="42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H28" s="42" t="n">
         <v>15</v>
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1534,7 +1534,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>
@@ -1576,11 +1576,11 @@
         <v>13</v>
       </c>
       <c r="H29" s="42" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="42" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K29" s="36" t="n"/>
       <c r="L29" s="18">
@@ -1595,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -1634,14 +1634,14 @@
       <c r="E30" s="35" t="n"/>
       <c r="F30" s="36" t="n"/>
       <c r="G30" s="42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H30" s="42" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="42" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K30" s="36" t="n"/>
       <c r="L30" s="18">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2035,14 +2035,14 @@
       <c r="E39" s="35" t="n"/>
       <c r="F39" s="36" t="n"/>
       <c r="G39" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="42" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K39" s="36" t="n"/>
       <c r="L39" s="18">
@@ -2057,7 +2057,7 @@
       <c r="O39" s="36" t="n"/>
       <c r="P39" s="42" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q39" s="35" t="n"/>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>75</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>79.56%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2163,14 +2163,14 @@
       <c r="E42" s="35" t="n"/>
       <c r="F42" s="36" t="n"/>
       <c r="G42" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="42" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K42" s="36" t="n"/>
       <c r="L42" s="18">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2217,14 +2217,14 @@
       <c r="E43" s="35" t="n"/>
       <c r="F43" s="36" t="n"/>
       <c r="G43" s="42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H43" s="42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" s="36" t="n"/>
       <c r="J43" s="42" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K43" s="36" t="n"/>
       <c r="L43" s="18">
@@ -2239,7 +2239,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>
@@ -2341,14 +2341,14 @@
       <c r="E46" s="35" t="n"/>
       <c r="F46" s="36" t="n"/>
       <c r="G46" s="42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H46" s="42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I46" s="36" t="n"/>
       <c r="J46" s="42" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K46" s="36" t="n"/>
       <c r="L46" s="18">
@@ -2363,7 +2363,7 @@
       <c r="O46" s="36" t="n"/>
       <c r="P46" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Q46" s="35" t="n"/>
@@ -2434,7 +2434,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>675</v>
+        <v>716</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2466,7 +2466,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>75</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2499,7 +2499,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>79.56%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1515,11 +1515,11 @@
         <v>16</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1573,14 +1573,14 @@
       <c r="E29" s="35" t="n"/>
       <c r="F29" s="36" t="n"/>
       <c r="G29" s="42" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" s="42" t="n">
         <v>13</v>
-      </c>
-      <c r="H29" s="42" t="n">
-        <v>14</v>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K29" s="36" t="n"/>
       <c r="L29" s="18">
@@ -1634,14 +1634,14 @@
       <c r="E30" s="35" t="n"/>
       <c r="F30" s="36" t="n"/>
       <c r="G30" s="42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H30" s="42" t="n">
         <v>19</v>
       </c>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="42" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K30" s="36" t="n"/>
       <c r="L30" s="18">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>79.56%</t>
+          <t>79.78%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="42" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K42" s="36" t="n"/>
       <c r="L42" s="18">
@@ -2220,11 +2220,11 @@
         <v>15</v>
       </c>
       <c r="H43" s="42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43" s="36" t="n"/>
       <c r="J43" s="42" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K43" s="36" t="n"/>
       <c r="L43" s="18">
@@ -2341,14 +2341,14 @@
       <c r="E46" s="35" t="n"/>
       <c r="F46" s="36" t="n"/>
       <c r="G46" s="42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H46" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="36" t="n"/>
       <c r="J46" s="42" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K46" s="36" t="n"/>
       <c r="L46" s="18">
@@ -2434,7 +2434,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2466,7 +2466,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>79.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2499,7 +2499,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>79.56%</t>
+          <t>79.78%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1519,7 +1519,7 @@
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1573,14 +1573,14 @@
       <c r="E29" s="35" t="n"/>
       <c r="F29" s="36" t="n"/>
       <c r="G29" s="42" t="n">
+        <v>13</v>
+      </c>
+      <c r="H29" s="42" t="n">
         <v>14</v>
-      </c>
-      <c r="H29" s="42" t="n">
-        <v>13</v>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="42" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K29" s="36" t="n"/>
       <c r="L29" s="18">
@@ -1634,14 +1634,14 @@
       <c r="E30" s="35" t="n"/>
       <c r="F30" s="36" t="n"/>
       <c r="G30" s="42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H30" s="42" t="n">
         <v>19</v>
       </c>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="42" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K30" s="36" t="n"/>
       <c r="L30" s="18">
@@ -2038,7 +2038,7 @@
         <v>17</v>
       </c>
       <c r="H39" s="42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="42" t="n">
@@ -2057,7 +2057,7 @@
       <c r="O39" s="36" t="n"/>
       <c r="P39" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Q39" s="35" t="n"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="42" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K42" s="36" t="n"/>
       <c r="L42" s="18">
@@ -2220,11 +2220,11 @@
         <v>15</v>
       </c>
       <c r="H43" s="42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" s="36" t="n"/>
       <c r="J43" s="42" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K43" s="36" t="n"/>
       <c r="L43" s="18">
@@ -2341,14 +2341,14 @@
       <c r="E46" s="35" t="n"/>
       <c r="F46" s="36" t="n"/>
       <c r="G46" s="42" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H46" s="42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" s="36" t="n"/>
       <c r="J46" s="42" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K46" s="36" t="n"/>
       <c r="L46" s="18">

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1875,14 +1875,14 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="42" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="42" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K35" s="36" t="n"/>
       <c r="L35" s="18">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1512,14 +1512,14 @@
       <c r="E28" s="35" t="n"/>
       <c r="F28" s="36" t="n"/>
       <c r="G28" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1534,7 +1534,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>
@@ -1573,14 +1573,14 @@
       <c r="E29" s="35" t="n"/>
       <c r="F29" s="36" t="n"/>
       <c r="G29" s="42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="42" t="n">
         <v>14</v>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="42" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K29" s="36" t="n"/>
       <c r="L29" s="18">
@@ -1595,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -1634,14 +1634,14 @@
       <c r="E30" s="35" t="n"/>
       <c r="F30" s="36" t="n"/>
       <c r="G30" s="42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H30" s="42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="42" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K30" s="36" t="n"/>
       <c r="L30" s="18">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2035,14 +2035,14 @@
       <c r="E39" s="35" t="n"/>
       <c r="F39" s="36" t="n"/>
       <c r="G39" s="42" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H39" s="42" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="36" t="n"/>
       <c r="J39" s="42" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K39" s="36" t="n"/>
       <c r="L39" s="18">
@@ -2057,7 +2057,7 @@
       <c r="O39" s="36" t="n"/>
       <c r="P39" s="42" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Q39" s="35" t="n"/>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>79.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>79.78%</t>
+          <t>83.56%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2163,14 +2163,14 @@
       <c r="E42" s="35" t="n"/>
       <c r="F42" s="36" t="n"/>
       <c r="G42" s="42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H42" s="42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K42" s="36" t="n"/>
       <c r="L42" s="18">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2217,14 +2217,14 @@
       <c r="E43" s="35" t="n"/>
       <c r="F43" s="36" t="n"/>
       <c r="G43" s="42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H43" s="42" t="n">
         <v>16</v>
       </c>
       <c r="I43" s="36" t="n"/>
       <c r="J43" s="42" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K43" s="36" t="n"/>
       <c r="L43" s="18">
@@ -2239,7 +2239,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>
@@ -2341,14 +2341,14 @@
       <c r="E46" s="35" t="n"/>
       <c r="F46" s="36" t="n"/>
       <c r="G46" s="42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H46" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="36" t="n"/>
       <c r="J46" s="42" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K46" s="36" t="n"/>
       <c r="L46" s="18">
@@ -2434,7 +2434,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2466,7 +2466,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>79.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2499,7 +2499,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>79.78%</t>
+          <t>83.56%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1512,14 +1512,14 @@
       <c r="E28" s="35" t="n"/>
       <c r="F28" s="36" t="n"/>
       <c r="G28" s="42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1634,14 +1634,14 @@
       <c r="E30" s="35" t="n"/>
       <c r="F30" s="36" t="n"/>
       <c r="G30" s="42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H30" s="42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I30" s="36" t="n"/>
       <c r="J30" s="42" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K30" s="36" t="n"/>
       <c r="L30" s="18">

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1512,14 +1512,14 @@
       <c r="E28" s="35" t="n"/>
       <c r="F28" s="36" t="n"/>
       <c r="G28" s="42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H28" s="42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -1534,7 +1534,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>
@@ -1573,14 +1573,14 @@
       <c r="E29" s="35" t="n"/>
       <c r="F29" s="36" t="n"/>
       <c r="G29" s="42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29" s="42" t="n">
         <v>14</v>
       </c>
       <c r="I29" s="36" t="n"/>
       <c r="J29" s="42" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K29" s="36" t="n"/>
       <c r="L29" s="18">
@@ -1595,7 +1595,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -1875,14 +1875,14 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="42" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="42" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K35" s="36" t="n"/>
       <c r="L35" s="18">
@@ -2166,7 +2166,7 @@
         <v>18</v>
       </c>
       <c r="H42" s="42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42" s="36" t="n"/>
       <c r="J42" s="42" t="n">
@@ -2217,14 +2217,14 @@
       <c r="E43" s="35" t="n"/>
       <c r="F43" s="36" t="n"/>
       <c r="G43" s="42" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H43" s="42" t="n">
         <v>16</v>
       </c>
       <c r="I43" s="36" t="n"/>
       <c r="J43" s="42" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K43" s="36" t="n"/>
       <c r="L43" s="18">
@@ -2239,7 +2239,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>
@@ -2341,14 +2341,14 @@
       <c r="E46" s="35" t="n"/>
       <c r="F46" s="36" t="n"/>
       <c r="G46" s="42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H46" s="42" t="n">
         <v>17</v>
       </c>
       <c r="I46" s="36" t="n"/>
       <c r="J46" s="42" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K46" s="36" t="n"/>
       <c r="L46" s="18">

--- a/report_cards/Report_Card_Balogun_Khadijat.xlsx
+++ b/report_cards/Report_Card_Balogun_Khadijat.xlsx
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M20" s="39" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="N20" s="30" t="n"/>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="I28" s="36" t="n"/>
       <c r="J28" s="42" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="18">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>83.56%</t>
+          <t>83.78%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="X42" s="43" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="Y42" s="30" t="n"/>
@@ -2434,7 +2434,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2466,7 +2466,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2499,7 +2499,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>83.56%</t>
+          <t>83.78%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2567,7 +2567,7 @@
       <c r="F52" s="36" t="n"/>
       <c r="G52" s="44" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>2nd</t>
         </is>
       </c>
       <c r="H52" s="35" t="n"/>
